--- a/高项记忆突击笔记.xlsx
+++ b/高项记忆突击笔记.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="85">
   <si>
     <t>十大管理</t>
   </si>
@@ -50,13 +50,19 @@
     <t>过程组</t>
   </si>
   <si>
-    <t>输入</t>
-  </si>
-  <si>
-    <t>工具</t>
-  </si>
-  <si>
-    <t>输出</t>
+    <t>口语解释</t>
+  </si>
+  <si>
+    <t>写作思路</t>
+  </si>
+  <si>
+    <t>核心输入</t>
+  </si>
+  <si>
+    <t>核心工具</t>
+  </si>
+  <si>
+    <t>核心输出</t>
   </si>
   <si>
     <t>项目整合管理</t>
@@ -65,24 +71,39 @@
     <t>制定项目章程</t>
   </si>
   <si>
+    <t>启动过程组</t>
+  </si>
+  <si>
     <t>制定项目管理计划</t>
   </si>
   <si>
+    <t>规划过程组</t>
+  </si>
+  <si>
     <t>指导与管理项目工作</t>
   </si>
   <si>
+    <t>执行过程组</t>
+  </si>
+  <si>
     <t>管理项目知识</t>
   </si>
   <si>
     <t>监控项目工作</t>
   </si>
   <si>
+    <t>监控过程组</t>
+  </si>
+  <si>
     <t>实施整体变更控制</t>
   </si>
   <si>
     <t>结束项目或阶段</t>
   </si>
   <si>
+    <t>收尾过程组</t>
+  </si>
+  <si>
     <t>项目范围管理</t>
   </si>
   <si>
@@ -102,6 +123,147 @@
   </si>
   <si>
     <t>控制范围</t>
+  </si>
+  <si>
+    <t>项目进度管理</t>
+  </si>
+  <si>
+    <t>规划进度管理</t>
+  </si>
+  <si>
+    <t>定义活动</t>
+  </si>
+  <si>
+    <t>排列活动顺序</t>
+  </si>
+  <si>
+    <t>估算活动执行时间</t>
+  </si>
+  <si>
+    <t>制定进度计划</t>
+  </si>
+  <si>
+    <t>控制进度</t>
+  </si>
+  <si>
+    <t>项目成本管理</t>
+  </si>
+  <si>
+    <t>规划成本管理</t>
+  </si>
+  <si>
+    <t>编写一个成本管理计划，
+指导成本管理的工作</t>
+  </si>
+  <si>
+    <t>写我组织了相关人员编写成本管理计划，
+还可以写编写计划的输入、工具、输出、
+方法、步骤</t>
+  </si>
+  <si>
+    <t>估算成本</t>
+  </si>
+  <si>
+    <t>制定预算</t>
+  </si>
+  <si>
+    <t>控制成本</t>
+  </si>
+  <si>
+    <t>项目质量管理</t>
+  </si>
+  <si>
+    <t>规划质量管理</t>
+  </si>
+  <si>
+    <t>管理质量</t>
+  </si>
+  <si>
+    <t>控制质量</t>
+  </si>
+  <si>
+    <t>项目资源管理</t>
+  </si>
+  <si>
+    <t>规划资源管理</t>
+  </si>
+  <si>
+    <t>估算活动资源</t>
+  </si>
+  <si>
+    <t>获取资源</t>
+  </si>
+  <si>
+    <t>建设团队</t>
+  </si>
+  <si>
+    <t>管理团队</t>
+  </si>
+  <si>
+    <t>控制资源</t>
+  </si>
+  <si>
+    <t>项目沟通管理</t>
+  </si>
+  <si>
+    <t>规划沟通管理</t>
+  </si>
+  <si>
+    <t>管理沟通</t>
+  </si>
+  <si>
+    <t>监督沟通</t>
+  </si>
+  <si>
+    <t>项目风险管理</t>
+  </si>
+  <si>
+    <t>规划风险管理</t>
+  </si>
+  <si>
+    <t>识别风险</t>
+  </si>
+  <si>
+    <t>实施定性风险管理</t>
+  </si>
+  <si>
+    <t>实施定量风险管理</t>
+  </si>
+  <si>
+    <t>规划风险应对</t>
+  </si>
+  <si>
+    <t>实施风险应对</t>
+  </si>
+  <si>
+    <t>监督风险</t>
+  </si>
+  <si>
+    <t>项目采购管理</t>
+  </si>
+  <si>
+    <t>规划采购管理</t>
+  </si>
+  <si>
+    <t>实施采购</t>
+  </si>
+  <si>
+    <t>控制采购</t>
+  </si>
+  <si>
+    <t>项目干系人管理</t>
+  </si>
+  <si>
+    <t>识别干系人</t>
+  </si>
+  <si>
+    <t>规划干系人管理</t>
+  </si>
+  <si>
+    <t>管理干系人参与</t>
+  </si>
+  <si>
+    <t>监督干系人参与</t>
   </si>
   <si>
     <t>立项管理</t>
@@ -507,12 +669,64 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="13">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -639,7 +853,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -651,34 +865,34 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
@@ -763,17 +977,38 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -847,8 +1082,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
@@ -1134,150 +1369,965 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A39:J52"/>
+  <dimension ref="A39:L88"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.875" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="9.875" customWidth="1"/>
     <col min="4" max="4" width="19.375" customWidth="1"/>
-    <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="9" max="9" width="9.375" customWidth="1"/>
+    <col min="5" max="5" width="10.875" customWidth="1"/>
+    <col min="8" max="8" width="21.5" customWidth="1"/>
+    <col min="9" max="9" width="17.625" customWidth="1"/>
+    <col min="11" max="11" width="9.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="39" spans="1:10">
-      <c r="A39" s="2" t="s">
+    <row r="39" spans="1:12">
+      <c r="A39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E39" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="G39" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H39" s="2" t="s">
+      <c r="H39" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I39" s="2" t="s">
+      <c r="I39" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J39" s="2" t="s">
+      <c r="J39" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="40" spans="1:10">
-      <c r="A40" s="3" t="s">
+      <c r="K39" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" t="s">
+      <c r="L39" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
-      <c r="A41" s="3"/>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" t="s">
+    <row r="40" spans="1:12">
+      <c r="A40" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" t="s">
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="43" spans="1:10">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" t="s">
+      <c r="E40" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="A44" s="3"/>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" t="s">
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" s="4"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="45" spans="1:10">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" t="s">
+      <c r="E41" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="46" spans="1:10">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" t="s">
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="47" spans="1:10">
-      <c r="A47" s="3" t="s">
+      <c r="E42" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D47" t="s">
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="48" spans="1:10">
-      <c r="A48" s="3"/>
-      <c r="D48" t="s">
+      <c r="E43" s="4"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" s="4"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="3"/>
-      <c r="D49" t="s">
+      <c r="E44" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="3"/>
-      <c r="D50" t="s">
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="3"/>
-      <c r="D51" t="s">
+      <c r="E45" s="4"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" s="4"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" s="3"/>
-      <c r="D52" t="s">
+      <c r="E46" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="A47" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48" s="4"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E48" s="4"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" s="4"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E49" s="4"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" s="4"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E50" s="4"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" s="4"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" s="4"/>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E52" s="4"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="A54" s="4"/>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E54" s="4"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="A55" s="4"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E55" s="4"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+    </row>
+    <row r="56" spans="1:12">
+      <c r="A56" s="4"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E56" s="4"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
+    </row>
+    <row r="57" spans="1:12">
+      <c r="A57" s="4"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E57" s="4"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+    </row>
+    <row r="58" spans="1:12">
+      <c r="A58" s="4"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+    </row>
+    <row r="59" ht="162" spans="1:12">
+      <c r="A59" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1"/>
+    </row>
+    <row r="60" spans="1:12">
+      <c r="A60" s="4"/>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E60" s="6"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1"/>
+    </row>
+    <row r="61" spans="1:12">
+      <c r="A61" s="4"/>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E61" s="7"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
+    </row>
+    <row r="62" spans="1:12">
+      <c r="A62" s="4"/>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1"/>
+    </row>
+    <row r="63" spans="1:12">
+      <c r="A63" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B63" s="8"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
+    </row>
+    <row r="64" spans="1:12">
+      <c r="A64" s="4"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
+      <c r="K64" s="1"/>
+      <c r="L64" s="1"/>
+    </row>
+    <row r="65" spans="1:12">
+      <c r="A65" s="4"/>
+      <c r="B65" s="10"/>
+      <c r="C65" s="10"/>
+      <c r="D65" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+    </row>
+    <row r="66" spans="1:12">
+      <c r="A66" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B66" s="8"/>
+      <c r="C66" s="8"/>
+      <c r="D66" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+    </row>
+    <row r="67" spans="1:12">
+      <c r="A67" s="4"/>
+      <c r="B67" s="9"/>
+      <c r="C67" s="9"/>
+      <c r="D67" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E67" s="4"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+    </row>
+    <row r="68" spans="1:12">
+      <c r="A68" s="4"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="9"/>
+      <c r="D68" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+    </row>
+    <row r="69" spans="1:12">
+      <c r="A69" s="4"/>
+      <c r="B69" s="9"/>
+      <c r="C69" s="9"/>
+      <c r="D69" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E69" s="4"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+    </row>
+    <row r="70" spans="1:12">
+      <c r="A70" s="4"/>
+      <c r="B70" s="9"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E70" s="4"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
+      <c r="L70" s="1"/>
+    </row>
+    <row r="71" spans="1:12">
+      <c r="A71" s="4"/>
+      <c r="B71" s="10"/>
+      <c r="C71" s="10"/>
+      <c r="D71" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
+      <c r="K71" s="1"/>
+      <c r="L71" s="1"/>
+    </row>
+    <row r="72" spans="1:12">
+      <c r="A72" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
+      <c r="K72" s="1"/>
+      <c r="L72" s="1"/>
+    </row>
+    <row r="73" spans="1:12">
+      <c r="A73" s="4"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
+      <c r="K73" s="1"/>
+      <c r="L73" s="1"/>
+    </row>
+    <row r="74" spans="1:12">
+      <c r="A74" s="4"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
+      <c r="K74" s="1"/>
+      <c r="L74" s="1"/>
+    </row>
+    <row r="75" spans="1:12">
+      <c r="A75" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+      <c r="K75" s="1"/>
+      <c r="L75" s="1"/>
+    </row>
+    <row r="76" spans="1:12">
+      <c r="A76" s="4"/>
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E76" s="4"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+      <c r="K76" s="1"/>
+      <c r="L76" s="1"/>
+    </row>
+    <row r="77" spans="1:12">
+      <c r="A77" s="4"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E77" s="4"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1"/>
+      <c r="L77" s="1"/>
+    </row>
+    <row r="78" spans="1:12">
+      <c r="A78" s="4"/>
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E78" s="4"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+      <c r="K78" s="1"/>
+      <c r="L78" s="1"/>
+    </row>
+    <row r="79" spans="1:12">
+      <c r="A79" s="4"/>
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E79" s="4"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
+      <c r="K79" s="1"/>
+      <c r="L79" s="1"/>
+    </row>
+    <row r="80" spans="1:12">
+      <c r="A80" s="4"/>
+      <c r="B80" s="4"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
+      <c r="K80" s="1"/>
+      <c r="L80" s="1"/>
+    </row>
+    <row r="81" spans="1:12">
+      <c r="A81" s="4"/>
+      <c r="B81" s="4"/>
+      <c r="C81" s="4"/>
+      <c r="D81" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
+      <c r="K81" s="1"/>
+      <c r="L81" s="1"/>
+    </row>
+    <row r="82" spans="1:12">
+      <c r="A82" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
+      <c r="K82" s="1"/>
+      <c r="L82" s="1"/>
+    </row>
+    <row r="83" spans="1:12">
+      <c r="A83" s="4"/>
+      <c r="B83" s="4"/>
+      <c r="C83" s="4"/>
+      <c r="D83" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
+      <c r="K83" s="1"/>
+      <c r="L83" s="1"/>
+    </row>
+    <row r="84" spans="1:12">
+      <c r="A84" s="4"/>
+      <c r="B84" s="4"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
+      <c r="K84" s="1"/>
+      <c r="L84" s="1"/>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="A85" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B85" s="8"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1"/>
+      <c r="K85" s="1"/>
+      <c r="L85" s="1"/>
+    </row>
+    <row r="86" spans="1:12">
+      <c r="A86" s="9"/>
+      <c r="B86" s="9"/>
+      <c r="C86" s="9"/>
+      <c r="D86" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
+      <c r="K86" s="1"/>
+      <c r="L86" s="1"/>
+    </row>
+    <row r="87" spans="1:12">
+      <c r="A87" s="9"/>
+      <c r="B87" s="9"/>
+      <c r="C87" s="9"/>
+      <c r="D87" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+      <c r="J87" s="1"/>
+      <c r="K87" s="1"/>
+      <c r="L87" s="1"/>
+    </row>
+    <row r="88" spans="1:12">
+      <c r="A88" s="10"/>
+      <c r="B88" s="10"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+      <c r="J88" s="1"/>
+      <c r="K88" s="1"/>
+      <c r="L88" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="39">
     <mergeCell ref="A40:A46"/>
     <mergeCell ref="A47:A52"/>
+    <mergeCell ref="A53:A58"/>
+    <mergeCell ref="A59:A62"/>
+    <mergeCell ref="A63:A65"/>
+    <mergeCell ref="A66:A71"/>
+    <mergeCell ref="A72:A74"/>
+    <mergeCell ref="A75:A81"/>
+    <mergeCell ref="A82:A84"/>
+    <mergeCell ref="A85:A88"/>
     <mergeCell ref="B40:B46"/>
+    <mergeCell ref="B47:B52"/>
+    <mergeCell ref="B53:B58"/>
+    <mergeCell ref="B59:B62"/>
+    <mergeCell ref="B63:B65"/>
+    <mergeCell ref="B66:B71"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="B75:B81"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="B85:B88"/>
     <mergeCell ref="C40:C46"/>
+    <mergeCell ref="C47:C52"/>
+    <mergeCell ref="C53:C58"/>
+    <mergeCell ref="C59:C62"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="C66:C71"/>
+    <mergeCell ref="C72:C74"/>
+    <mergeCell ref="C75:C81"/>
+    <mergeCell ref="C82:C84"/>
+    <mergeCell ref="C85:C88"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="E47:E50"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="E53:E57"/>
+    <mergeCell ref="E59:E61"/>
+    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="E68:E70"/>
+    <mergeCell ref="E75:E79"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1316,43 +2366,47 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="2"/>
   <cols>
+    <col min="1" max="1" width="10.875" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="24.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="54" spans="1:3">
-      <c r="A1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>25</v>
+      <c r="A1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="2" ht="54" spans="1:3">
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>27</v>
+      <c r="A2" s="1"/>
+      <c r="B2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="3" ht="67.5" spans="1:3">
-      <c r="B3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>29</v>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="4" ht="54" spans="1:3">
-      <c r="B4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>31</v>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/高项记忆突击笔记.xlsx
+++ b/高项记忆突击笔记.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" firstSheet="2"/>
+    <workbookView windowWidth="28800" windowHeight="12375" firstSheet="2" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="五大过程十大管理" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="98">
   <si>
     <t>十大管理</t>
   </si>
@@ -272,38 +272,64 @@
     <t>项目投资前四个阶段</t>
   </si>
   <si>
-    <t>1）项目建议与立项申请
-2）初步可行性研究
-3）详细可行性研究
-4）评估与决策</t>
+    <t>1）项目建议与立项申请</t>
+  </si>
+  <si>
+    <t>2）初步可行性研究</t>
+  </si>
+  <si>
+    <t>3）详细可行性研究</t>
+  </si>
+  <si>
+    <t>4）评估与决策</t>
   </si>
   <si>
     <t>项目建议书内容【简述-两必两预测】</t>
   </si>
   <si>
-    <t>1）项目的必要性
-2）项目的市场预测
-3）项目预期成果的市场预测
-4）项目建设的必要条件</t>
+    <t>1）项目的必要性</t>
+  </si>
+  <si>
+    <t>2）项目的市场预测</t>
+  </si>
+  <si>
+    <t>3）项目预期成果的市场预测</t>
+  </si>
+  <si>
+    <t>4）项目建设的必要条件</t>
   </si>
   <si>
     <t>可行性研究的内容【可研-鸡精摄晕他】</t>
   </si>
   <si>
-    <t>1）技术可行性分析
-2）经济可行性分析
-3）社会效益可行性分析
-4）运行环境可行性分析
-5）其他方面可行性分析</t>
-  </si>
-  <si>
-    <t>技术可行性分析内容【饥渴-风效能用】</t>
-  </si>
-  <si>
-    <t>1）进行项目开发的风险
-2）人力资源的有效性
-3）技术能力的可能性
-4）物资（产品）的可用性</t>
+    <t>1）技术可行性分析</t>
+  </si>
+  <si>
+    <t>2）经济可行性分析</t>
+  </si>
+  <si>
+    <t>3）社会效益可行性分析</t>
+  </si>
+  <si>
+    <t>4）运行环境可行性分析</t>
+  </si>
+  <si>
+    <t>5）其他方面可行性分析</t>
+  </si>
+  <si>
+    <t>技术可行性分析内容【饥渴-嫌小能用】</t>
+  </si>
+  <si>
+    <t>1）进行项目开发的风险</t>
+  </si>
+  <si>
+    <t>2）人力资源的有效性</t>
+  </si>
+  <si>
+    <t>3）技术能力的可能性</t>
+  </si>
+  <si>
+    <t>4）物资（产品）的可用性</t>
   </si>
 </sst>
 </file>
@@ -469,7 +495,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -478,6 +504,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -669,7 +701,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -690,6 +722,17 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -853,7 +896,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -865,150 +908,162 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1382,910 +1437,910 @@
   </cols>
   <sheetData>
     <row r="39" spans="1:12">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="E39" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F39" s="3" t="s">
+      <c r="F39" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="G39" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="H39" s="3" t="s">
+      <c r="H39" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I39" s="3" t="s">
+      <c r="I39" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="J39" s="3" t="s">
+      <c r="J39" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="K39" s="3" t="s">
+      <c r="K39" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="L39" s="3" t="s">
+      <c r="L39" s="10" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="1" t="s">
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="7"/>
+      <c r="J40" s="7"/>
+      <c r="K40" s="7"/>
+      <c r="L40" s="7"/>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="1" t="s">
+      <c r="A41" s="11"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="7"/>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="1" t="s">
+      <c r="A42" s="11"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E42" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="7"/>
+      <c r="K42" s="7"/>
+      <c r="L42" s="7"/>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="1" t="s">
+      <c r="A43" s="11"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E43" s="4"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="7"/>
+      <c r="J43" s="7"/>
+      <c r="K43" s="7"/>
+      <c r="L43" s="7"/>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="4"/>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="1" t="s">
+      <c r="A44" s="11"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="7"/>
+      <c r="J44" s="7"/>
+      <c r="K44" s="7"/>
+      <c r="L44" s="7"/>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="4"/>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="1" t="s">
+      <c r="A45" s="11"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E45" s="4"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
+      <c r="K45" s="7"/>
+      <c r="L45" s="7"/>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="4"/>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="1" t="s">
+      <c r="A46" s="11"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="7"/>
+      <c r="J46" s="7"/>
+      <c r="K46" s="7"/>
+      <c r="L46" s="7"/>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="1" t="s">
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="7"/>
+      <c r="K47" s="7"/>
+      <c r="L47" s="7"/>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="4"/>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="1" t="s">
+      <c r="A48" s="11"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E48" s="4"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="7"/>
+      <c r="J48" s="7"/>
+      <c r="K48" s="7"/>
+      <c r="L48" s="7"/>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="4"/>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="1" t="s">
+      <c r="A49" s="11"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E49" s="4"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="7"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="7"/>
+      <c r="L49" s="7"/>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="4"/>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="1" t="s">
+      <c r="A50" s="11"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E50" s="4"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="7"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="7"/>
+      <c r="K50" s="7"/>
+      <c r="L50" s="7"/>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="4"/>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="1" t="s">
+      <c r="A51" s="11"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="E51" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="1"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="7"/>
+      <c r="K51" s="7"/>
+      <c r="L51" s="7"/>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="4"/>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="1" t="s">
+      <c r="A52" s="11"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E52" s="4"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="7"/>
+      <c r="G52" s="7"/>
+      <c r="H52" s="7"/>
+      <c r="I52" s="7"/>
+      <c r="J52" s="7"/>
+      <c r="K52" s="7"/>
+      <c r="L52" s="7"/>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="1" t="s">
+      <c r="B53" s="11"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E53" s="4" t="s">
+      <c r="E53" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
-      <c r="L53" s="1"/>
+      <c r="F53" s="7"/>
+      <c r="G53" s="7"/>
+      <c r="H53" s="7"/>
+      <c r="I53" s="7"/>
+      <c r="J53" s="7"/>
+      <c r="K53" s="7"/>
+      <c r="L53" s="7"/>
     </row>
     <row r="54" spans="1:12">
-      <c r="A54" s="4"/>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="1" t="s">
+      <c r="A54" s="11"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E54" s="4"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="7"/>
+      <c r="J54" s="7"/>
+      <c r="K54" s="7"/>
+      <c r="L54" s="7"/>
     </row>
     <row r="55" spans="1:12">
-      <c r="A55" s="4"/>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="1" t="s">
+      <c r="A55" s="11"/>
+      <c r="B55" s="11"/>
+      <c r="C55" s="11"/>
+      <c r="D55" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E55" s="4"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
-      <c r="L55" s="1"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="7"/>
+      <c r="K55" s="7"/>
+      <c r="L55" s="7"/>
     </row>
     <row r="56" spans="1:12">
-      <c r="A56" s="4"/>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="1" t="s">
+      <c r="A56" s="11"/>
+      <c r="B56" s="11"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E56" s="4"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
-      <c r="L56" s="1"/>
+      <c r="E56" s="11"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7"/>
+      <c r="J56" s="7"/>
+      <c r="K56" s="7"/>
+      <c r="L56" s="7"/>
     </row>
     <row r="57" spans="1:12">
-      <c r="A57" s="4"/>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="1" t="s">
+      <c r="A57" s="11"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E57" s="4"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="1"/>
+      <c r="E57" s="11"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="7"/>
+      <c r="H57" s="7"/>
+      <c r="I57" s="7"/>
+      <c r="J57" s="7"/>
+      <c r="K57" s="7"/>
+      <c r="L57" s="7"/>
     </row>
     <row r="58" spans="1:12">
-      <c r="A58" s="4"/>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="1" t="s">
+      <c r="A58" s="11"/>
+      <c r="B58" s="11"/>
+      <c r="C58" s="11"/>
+      <c r="D58" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E58" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
-      <c r="L58" s="1"/>
-    </row>
-    <row r="59" ht="162" spans="1:12">
-      <c r="A59" s="4" t="s">
+      <c r="F58" s="7"/>
+      <c r="G58" s="7"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="7"/>
+      <c r="J58" s="7"/>
+      <c r="K58" s="7"/>
+      <c r="L58" s="7"/>
+    </row>
+    <row r="59" ht="67.5" spans="1:12">
+      <c r="A59" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="1" t="s">
+      <c r="B59" s="11"/>
+      <c r="C59" s="11"/>
+      <c r="D59" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E59" s="5" t="s">
+      <c r="E59" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="2" t="s">
+      <c r="F59" s="7"/>
+      <c r="G59" s="7"/>
+      <c r="H59" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="I59" s="2" t="s">
+      <c r="I59" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="J59" s="1"/>
-      <c r="K59" s="1"/>
-      <c r="L59" s="1"/>
+      <c r="J59" s="7"/>
+      <c r="K59" s="7"/>
+      <c r="L59" s="7"/>
     </row>
     <row r="60" spans="1:12">
-      <c r="A60" s="4"/>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="1" t="s">
+      <c r="A60" s="11"/>
+      <c r="B60" s="11"/>
+      <c r="C60" s="11"/>
+      <c r="D60" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E60" s="6"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="1"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="7"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="7"/>
+      <c r="J60" s="7"/>
+      <c r="K60" s="7"/>
+      <c r="L60" s="7"/>
     </row>
     <row r="61" spans="1:12">
-      <c r="A61" s="4"/>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="1" t="s">
+      <c r="A61" s="11"/>
+      <c r="B61" s="11"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E61" s="7"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
-      <c r="L61" s="1"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="7"/>
+      <c r="H61" s="7"/>
+      <c r="I61" s="7"/>
+      <c r="J61" s="7"/>
+      <c r="K61" s="7"/>
+      <c r="L61" s="7"/>
     </row>
     <row r="62" spans="1:12">
-      <c r="A62" s="4"/>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="1" t="s">
+      <c r="A62" s="11"/>
+      <c r="B62" s="11"/>
+      <c r="C62" s="11"/>
+      <c r="D62" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E62" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="1"/>
+      <c r="F62" s="7"/>
+      <c r="G62" s="7"/>
+      <c r="H62" s="7"/>
+      <c r="I62" s="7"/>
+      <c r="J62" s="7"/>
+      <c r="K62" s="7"/>
+      <c r="L62" s="7"/>
     </row>
     <row r="63" spans="1:12">
-      <c r="A63" s="4" t="s">
+      <c r="A63" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B63" s="8"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="1" t="s">
+      <c r="B63" s="12"/>
+      <c r="C63" s="12"/>
+      <c r="D63" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E63" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
-      <c r="J63" s="1"/>
-      <c r="K63" s="1"/>
-      <c r="L63" s="1"/>
+      <c r="F63" s="7"/>
+      <c r="G63" s="7"/>
+      <c r="H63" s="7"/>
+      <c r="I63" s="7"/>
+      <c r="J63" s="7"/>
+      <c r="K63" s="7"/>
+      <c r="L63" s="7"/>
     </row>
     <row r="64" spans="1:12">
-      <c r="A64" s="4"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="1" t="s">
+      <c r="A64" s="11"/>
+      <c r="B64" s="13"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="E64" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="1"/>
-      <c r="K64" s="1"/>
-      <c r="L64" s="1"/>
+      <c r="F64" s="7"/>
+      <c r="G64" s="7"/>
+      <c r="H64" s="7"/>
+      <c r="I64" s="7"/>
+      <c r="J64" s="7"/>
+      <c r="K64" s="7"/>
+      <c r="L64" s="7"/>
     </row>
     <row r="65" spans="1:12">
-      <c r="A65" s="4"/>
-      <c r="B65" s="10"/>
-      <c r="C65" s="10"/>
-      <c r="D65" s="1" t="s">
+      <c r="A65" s="11"/>
+      <c r="B65" s="14"/>
+      <c r="C65" s="14"/>
+      <c r="D65" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="E65" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-      <c r="J65" s="1"/>
-      <c r="K65" s="1"/>
-      <c r="L65" s="1"/>
+      <c r="F65" s="7"/>
+      <c r="G65" s="7"/>
+      <c r="H65" s="7"/>
+      <c r="I65" s="7"/>
+      <c r="J65" s="7"/>
+      <c r="K65" s="7"/>
+      <c r="L65" s="7"/>
     </row>
     <row r="66" spans="1:12">
-      <c r="A66" s="4" t="s">
+      <c r="A66" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B66" s="8"/>
-      <c r="C66" s="8"/>
-      <c r="D66" s="1" t="s">
+      <c r="B66" s="12"/>
+      <c r="C66" s="12"/>
+      <c r="D66" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E66" s="4" t="s">
+      <c r="E66" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
-      <c r="L66" s="1"/>
+      <c r="F66" s="7"/>
+      <c r="G66" s="7"/>
+      <c r="H66" s="7"/>
+      <c r="I66" s="7"/>
+      <c r="J66" s="7"/>
+      <c r="K66" s="7"/>
+      <c r="L66" s="7"/>
     </row>
     <row r="67" spans="1:12">
-      <c r="A67" s="4"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="1" t="s">
+      <c r="A67" s="11"/>
+      <c r="B67" s="13"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E67" s="4"/>
-      <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
-      <c r="K67" s="1"/>
-      <c r="L67" s="1"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="7"/>
+      <c r="G67" s="7"/>
+      <c r="H67" s="7"/>
+      <c r="I67" s="7"/>
+      <c r="J67" s="7"/>
+      <c r="K67" s="7"/>
+      <c r="L67" s="7"/>
     </row>
     <row r="68" spans="1:12">
-      <c r="A68" s="4"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="1" t="s">
+      <c r="A68" s="11"/>
+      <c r="B68" s="13"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E68" s="4" t="s">
+      <c r="E68" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
-      <c r="L68" s="1"/>
+      <c r="F68" s="7"/>
+      <c r="G68" s="7"/>
+      <c r="H68" s="7"/>
+      <c r="I68" s="7"/>
+      <c r="J68" s="7"/>
+      <c r="K68" s="7"/>
+      <c r="L68" s="7"/>
     </row>
     <row r="69" spans="1:12">
-      <c r="A69" s="4"/>
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="1" t="s">
+      <c r="A69" s="11"/>
+      <c r="B69" s="13"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E69" s="4"/>
-      <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
-      <c r="K69" s="1"/>
-      <c r="L69" s="1"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="7"/>
+      <c r="G69" s="7"/>
+      <c r="H69" s="7"/>
+      <c r="I69" s="7"/>
+      <c r="J69" s="7"/>
+      <c r="K69" s="7"/>
+      <c r="L69" s="7"/>
     </row>
     <row r="70" spans="1:12">
-      <c r="A70" s="4"/>
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="1" t="s">
+      <c r="A70" s="11"/>
+      <c r="B70" s="13"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="E70" s="4"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
-      <c r="K70" s="1"/>
-      <c r="L70" s="1"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="7"/>
+      <c r="G70" s="7"/>
+      <c r="H70" s="7"/>
+      <c r="I70" s="7"/>
+      <c r="J70" s="7"/>
+      <c r="K70" s="7"/>
+      <c r="L70" s="7"/>
     </row>
     <row r="71" spans="1:12">
-      <c r="A71" s="4"/>
-      <c r="B71" s="10"/>
-      <c r="C71" s="10"/>
-      <c r="D71" s="1" t="s">
+      <c r="A71" s="11"/>
+      <c r="B71" s="14"/>
+      <c r="C71" s="14"/>
+      <c r="D71" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="E71" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-      <c r="J71" s="1"/>
-      <c r="K71" s="1"/>
-      <c r="L71" s="1"/>
+      <c r="F71" s="7"/>
+      <c r="G71" s="7"/>
+      <c r="H71" s="7"/>
+      <c r="I71" s="7"/>
+      <c r="J71" s="7"/>
+      <c r="K71" s="7"/>
+      <c r="L71" s="7"/>
     </row>
     <row r="72" spans="1:12">
-      <c r="A72" s="4" t="s">
+      <c r="A72" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="1" t="s">
+      <c r="B72" s="11"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="E72" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
-      <c r="J72" s="1"/>
-      <c r="K72" s="1"/>
-      <c r="L72" s="1"/>
+      <c r="F72" s="7"/>
+      <c r="G72" s="7"/>
+      <c r="H72" s="7"/>
+      <c r="I72" s="7"/>
+      <c r="J72" s="7"/>
+      <c r="K72" s="7"/>
+      <c r="L72" s="7"/>
     </row>
     <row r="73" spans="1:12">
-      <c r="A73" s="4"/>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="1" t="s">
+      <c r="A73" s="11"/>
+      <c r="B73" s="11"/>
+      <c r="C73" s="11"/>
+      <c r="D73" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="E73" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="1"/>
-      <c r="K73" s="1"/>
-      <c r="L73" s="1"/>
+      <c r="F73" s="7"/>
+      <c r="G73" s="7"/>
+      <c r="H73" s="7"/>
+      <c r="I73" s="7"/>
+      <c r="J73" s="7"/>
+      <c r="K73" s="7"/>
+      <c r="L73" s="7"/>
     </row>
     <row r="74" spans="1:12">
-      <c r="A74" s="4"/>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="1" t="s">
+      <c r="A74" s="11"/>
+      <c r="B74" s="11"/>
+      <c r="C74" s="11"/>
+      <c r="D74" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="E74" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
-      <c r="J74" s="1"/>
-      <c r="K74" s="1"/>
-      <c r="L74" s="1"/>
+      <c r="F74" s="7"/>
+      <c r="G74" s="7"/>
+      <c r="H74" s="7"/>
+      <c r="I74" s="7"/>
+      <c r="J74" s="7"/>
+      <c r="K74" s="7"/>
+      <c r="L74" s="7"/>
     </row>
     <row r="75" spans="1:12">
-      <c r="A75" s="4" t="s">
+      <c r="A75" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="1" t="s">
+      <c r="B75" s="11"/>
+      <c r="C75" s="11"/>
+      <c r="D75" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E75" s="4" t="s">
+      <c r="E75" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
-      <c r="J75" s="1"/>
-      <c r="K75" s="1"/>
-      <c r="L75" s="1"/>
+      <c r="F75" s="7"/>
+      <c r="G75" s="7"/>
+      <c r="H75" s="7"/>
+      <c r="I75" s="7"/>
+      <c r="J75" s="7"/>
+      <c r="K75" s="7"/>
+      <c r="L75" s="7"/>
     </row>
     <row r="76" spans="1:12">
-      <c r="A76" s="4"/>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="1" t="s">
+      <c r="A76" s="11"/>
+      <c r="B76" s="11"/>
+      <c r="C76" s="11"/>
+      <c r="D76" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E76" s="4"/>
-      <c r="F76" s="1"/>
-      <c r="G76" s="1"/>
-      <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
-      <c r="J76" s="1"/>
-      <c r="K76" s="1"/>
-      <c r="L76" s="1"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="7"/>
+      <c r="G76" s="7"/>
+      <c r="H76" s="7"/>
+      <c r="I76" s="7"/>
+      <c r="J76" s="7"/>
+      <c r="K76" s="7"/>
+      <c r="L76" s="7"/>
     </row>
     <row r="77" spans="1:12">
-      <c r="A77" s="4"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="1" t="s">
+      <c r="A77" s="11"/>
+      <c r="B77" s="11"/>
+      <c r="C77" s="11"/>
+      <c r="D77" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E77" s="4"/>
-      <c r="F77" s="1"/>
-      <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
-      <c r="J77" s="1"/>
-      <c r="K77" s="1"/>
-      <c r="L77" s="1"/>
+      <c r="E77" s="11"/>
+      <c r="F77" s="7"/>
+      <c r="G77" s="7"/>
+      <c r="H77" s="7"/>
+      <c r="I77" s="7"/>
+      <c r="J77" s="7"/>
+      <c r="K77" s="7"/>
+      <c r="L77" s="7"/>
     </row>
     <row r="78" spans="1:12">
-      <c r="A78" s="4"/>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="1" t="s">
+      <c r="A78" s="11"/>
+      <c r="B78" s="11"/>
+      <c r="C78" s="11"/>
+      <c r="D78" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E78" s="4"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="1"/>
-      <c r="K78" s="1"/>
-      <c r="L78" s="1"/>
+      <c r="E78" s="11"/>
+      <c r="F78" s="7"/>
+      <c r="G78" s="7"/>
+      <c r="H78" s="7"/>
+      <c r="I78" s="7"/>
+      <c r="J78" s="7"/>
+      <c r="K78" s="7"/>
+      <c r="L78" s="7"/>
     </row>
     <row r="79" spans="1:12">
-      <c r="A79" s="4"/>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="1" t="s">
+      <c r="A79" s="11"/>
+      <c r="B79" s="11"/>
+      <c r="C79" s="11"/>
+      <c r="D79" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E79" s="4"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="1"/>
-      <c r="H79" s="1"/>
-      <c r="I79" s="1"/>
-      <c r="J79" s="1"/>
-      <c r="K79" s="1"/>
-      <c r="L79" s="1"/>
+      <c r="E79" s="11"/>
+      <c r="F79" s="7"/>
+      <c r="G79" s="7"/>
+      <c r="H79" s="7"/>
+      <c r="I79" s="7"/>
+      <c r="J79" s="7"/>
+      <c r="K79" s="7"/>
+      <c r="L79" s="7"/>
     </row>
     <row r="80" spans="1:12">
-      <c r="A80" s="4"/>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="1" t="s">
+      <c r="A80" s="11"/>
+      <c r="B80" s="11"/>
+      <c r="C80" s="11"/>
+      <c r="D80" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E80" s="1" t="s">
+      <c r="E80" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F80" s="1"/>
-      <c r="G80" s="1"/>
-      <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
-      <c r="J80" s="1"/>
-      <c r="K80" s="1"/>
-      <c r="L80" s="1"/>
+      <c r="F80" s="7"/>
+      <c r="G80" s="7"/>
+      <c r="H80" s="7"/>
+      <c r="I80" s="7"/>
+      <c r="J80" s="7"/>
+      <c r="K80" s="7"/>
+      <c r="L80" s="7"/>
     </row>
     <row r="81" spans="1:12">
-      <c r="A81" s="4"/>
-      <c r="B81" s="4"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="1" t="s">
+      <c r="A81" s="11"/>
+      <c r="B81" s="11"/>
+      <c r="C81" s="11"/>
+      <c r="D81" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E81" s="1" t="s">
+      <c r="E81" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="1"/>
-      <c r="K81" s="1"/>
-      <c r="L81" s="1"/>
+      <c r="F81" s="7"/>
+      <c r="G81" s="7"/>
+      <c r="H81" s="7"/>
+      <c r="I81" s="7"/>
+      <c r="J81" s="7"/>
+      <c r="K81" s="7"/>
+      <c r="L81" s="7"/>
     </row>
     <row r="82" spans="1:12">
-      <c r="A82" s="4" t="s">
+      <c r="A82" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="4"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="1" t="s">
+      <c r="B82" s="11"/>
+      <c r="C82" s="11"/>
+      <c r="D82" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E82" s="1" t="s">
+      <c r="E82" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
-      <c r="H82" s="1"/>
-      <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
-      <c r="K82" s="1"/>
-      <c r="L82" s="1"/>
+      <c r="F82" s="7"/>
+      <c r="G82" s="7"/>
+      <c r="H82" s="7"/>
+      <c r="I82" s="7"/>
+      <c r="J82" s="7"/>
+      <c r="K82" s="7"/>
+      <c r="L82" s="7"/>
     </row>
     <row r="83" spans="1:12">
-      <c r="A83" s="4"/>
-      <c r="B83" s="4"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="1" t="s">
+      <c r="A83" s="11"/>
+      <c r="B83" s="11"/>
+      <c r="C83" s="11"/>
+      <c r="D83" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E83" s="1" t="s">
+      <c r="E83" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F83" s="1"/>
-      <c r="G83" s="1"/>
-      <c r="H83" s="1"/>
-      <c r="I83" s="1"/>
-      <c r="J83" s="1"/>
-      <c r="K83" s="1"/>
-      <c r="L83" s="1"/>
+      <c r="F83" s="7"/>
+      <c r="G83" s="7"/>
+      <c r="H83" s="7"/>
+      <c r="I83" s="7"/>
+      <c r="J83" s="7"/>
+      <c r="K83" s="7"/>
+      <c r="L83" s="7"/>
     </row>
     <row r="84" spans="1:12">
-      <c r="A84" s="4"/>
-      <c r="B84" s="4"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="1" t="s">
+      <c r="A84" s="11"/>
+      <c r="B84" s="11"/>
+      <c r="C84" s="11"/>
+      <c r="D84" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E84" s="1" t="s">
+      <c r="E84" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F84" s="1"/>
-      <c r="G84" s="1"/>
-      <c r="H84" s="1"/>
-      <c r="I84" s="1"/>
-      <c r="J84" s="1"/>
-      <c r="K84" s="1"/>
-      <c r="L84" s="1"/>
+      <c r="F84" s="7"/>
+      <c r="G84" s="7"/>
+      <c r="H84" s="7"/>
+      <c r="I84" s="7"/>
+      <c r="J84" s="7"/>
+      <c r="K84" s="7"/>
+      <c r="L84" s="7"/>
     </row>
     <row r="85" spans="1:12">
-      <c r="A85" s="8" t="s">
+      <c r="A85" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B85" s="8"/>
-      <c r="C85" s="8"/>
-      <c r="D85" s="1" t="s">
+      <c r="B85" s="12"/>
+      <c r="C85" s="12"/>
+      <c r="D85" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E85" s="1" t="s">
+      <c r="E85" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F85" s="1"/>
-      <c r="G85" s="1"/>
-      <c r="H85" s="1"/>
-      <c r="I85" s="1"/>
-      <c r="J85" s="1"/>
-      <c r="K85" s="1"/>
-      <c r="L85" s="1"/>
+      <c r="F85" s="7"/>
+      <c r="G85" s="7"/>
+      <c r="H85" s="7"/>
+      <c r="I85" s="7"/>
+      <c r="J85" s="7"/>
+      <c r="K85" s="7"/>
+      <c r="L85" s="7"/>
     </row>
     <row r="86" spans="1:12">
-      <c r="A86" s="9"/>
-      <c r="B86" s="9"/>
-      <c r="C86" s="9"/>
-      <c r="D86" s="1" t="s">
+      <c r="A86" s="13"/>
+      <c r="B86" s="13"/>
+      <c r="C86" s="13"/>
+      <c r="D86" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E86" s="1" t="s">
+      <c r="E86" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F86" s="1"/>
-      <c r="G86" s="1"/>
-      <c r="H86" s="1"/>
-      <c r="I86" s="1"/>
-      <c r="J86" s="1"/>
-      <c r="K86" s="1"/>
-      <c r="L86" s="1"/>
+      <c r="F86" s="7"/>
+      <c r="G86" s="7"/>
+      <c r="H86" s="7"/>
+      <c r="I86" s="7"/>
+      <c r="J86" s="7"/>
+      <c r="K86" s="7"/>
+      <c r="L86" s="7"/>
     </row>
     <row r="87" spans="1:12">
-      <c r="A87" s="9"/>
-      <c r="B87" s="9"/>
-      <c r="C87" s="9"/>
-      <c r="D87" s="1" t="s">
+      <c r="A87" s="13"/>
+      <c r="B87" s="13"/>
+      <c r="C87" s="13"/>
+      <c r="D87" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E87" s="1" t="s">
+      <c r="E87" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F87" s="1"/>
-      <c r="G87" s="1"/>
-      <c r="H87" s="1"/>
-      <c r="I87" s="1"/>
-      <c r="J87" s="1"/>
-      <c r="K87" s="1"/>
-      <c r="L87" s="1"/>
+      <c r="F87" s="7"/>
+      <c r="G87" s="7"/>
+      <c r="H87" s="7"/>
+      <c r="I87" s="7"/>
+      <c r="J87" s="7"/>
+      <c r="K87" s="7"/>
+      <c r="L87" s="7"/>
     </row>
     <row r="88" spans="1:12">
-      <c r="A88" s="10"/>
-      <c r="B88" s="10"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="1" t="s">
+      <c r="A88" s="14"/>
+      <c r="B88" s="14"/>
+      <c r="C88" s="14"/>
+      <c r="D88" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E88" s="1" t="s">
+      <c r="E88" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F88" s="1"/>
-      <c r="G88" s="1"/>
-      <c r="H88" s="1"/>
-      <c r="I88" s="1"/>
-      <c r="J88" s="1"/>
-      <c r="K88" s="1"/>
-      <c r="L88" s="1"/>
+      <c r="F88" s="7"/>
+      <c r="G88" s="7"/>
+      <c r="H88" s="7"/>
+      <c r="I88" s="7"/>
+      <c r="J88" s="7"/>
+      <c r="K88" s="7"/>
+      <c r="L88" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="39">
@@ -2363,53 +2418,200 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="2"/>
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="10.875" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="24.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="54" spans="1:3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="3"/>
+      <c r="B2" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C2" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="2" ht="54" spans="1:3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
+    <row r="3" spans="1:3">
+      <c r="A3" s="6"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="2" t="s">
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="6"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" ht="67.5" spans="1:3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1" t="s">
+    <row r="5" spans="1:3">
+      <c r="A5" s="6"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C3" s="2" t="s">
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="5"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="6"/>
+      <c r="B7" s="4" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="4" ht="54" spans="1:3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1" t="s">
+      <c r="C7" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C4" s="2" t="s">
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="6"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="5" t="s">
         <v>84</v>
       </c>
     </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="6"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="6"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="6"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="5"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="6"/>
+      <c r="B12" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="6"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="6"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="6"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="6"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="6"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="5"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="9"/>
+      <c r="B18" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="9"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="9"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="9"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="9"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="9"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="9"/>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="9"/>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="9"/>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="9"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="9"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="9"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="9"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="9"/>
+    </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="B18:B21"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
